--- a/Digimatic_analyse/res/Digimatic_Tabelle.xlsx
+++ b/Digimatic_analyse/res/Digimatic_Tabelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_docs\notes\Digimatic_analyse\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AF27B9-60DD-41A1-B832-ED889AE3BCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C715F7A-48E2-46D8-8874-2D880775D6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="555" yWindow="450" windowWidth="27945" windowHeight="16425" xr2:uid="{3E82B335-DAA8-4F32-B234-7C205CAED7F1}"/>
   </bookViews>
